--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -412,24 +412,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>salary</v>
+        <v>Business</v>
       </c>
       <c r="B2">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>freelance</v>
+        <v>Job</v>
       </c>
       <c r="B3">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-03-18</v>
+        <v>2026-04-08</v>
       </c>
     </row>
   </sheetData>
